--- a/data/macro/USA/FOMC Dot Plot data.xlsx
+++ b/data/macro/USA/FOMC Dot Plot data.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C28EE6-B2F4-4964-8280-0C7D049F6C59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C28EE6-B2F4-4964-8280-0C7D049F6C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FOMCDOT" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -125,36 +136,36 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -179,9 +190,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -219,9 +230,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -254,26 +265,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -306,26 +300,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -500,16 +477,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H1499"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="12" customWidth="1"/>
     <col min="4" max="4" width="14" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" style="7" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
